--- a/Train_A_Skill/Level1_Train_A_Skill.xlsx
+++ b/Train_A_Skill/Level1_Train_A_Skill.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEST" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Phase 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TEST" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -138,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -172,9 +173,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -571,10 +569,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each block is one skill — train only the skill you are chasing. Phase 1 = the 0 exercises + the grade 1 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Each block is one skill — train only the skill you are chasing. Skills have different numbers of phases (set by the grades on the skill ladder); a skill only appears on the phase tabs it has. Phase 1 = that skill's 0 exercises + its grade 1 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -599,7 +597,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  PHASE 1 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -790,7 +788,7 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  2 sets</t>
+          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  PHASE 1 of 3  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -981,7 +979,7 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  2 sets</t>
+          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  PHASE 1 of 3  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1148,7 @@
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 1 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1185,7 @@
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 1 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1310,7 @@
     <row r="49" ht="18.75" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  2 sets</t>
+          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  PHASE 1 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1501,7 @@
     <row r="60" ht="18.75" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  3 sets</t>
+          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  PHASE 1 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1604,7 @@
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  3 sets</t>
+          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  PHASE 1 of 3  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1707,7 @@
     <row r="74" ht="18.75" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  3 sets</t>
+          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  PHASE 1 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -1812,7 +1810,7 @@
     <row r="81" ht="18.75" customHeight="1">
       <c r="A81" s="4" t="inlineStr">
         <is>
-          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  3 sets</t>
+          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  PHASE 1 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1869,7 @@
     <row r="86" ht="18.75" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  3 sets</t>
+          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  PHASE 1 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -2308,10 +2306,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each block is one skill — train only the skill you are chasing. Phase 2 = the 0 exercises + the grade 2 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Each block is one skill — train only the skill you are chasing. Skills have different numbers of phases (set by the grades on the skill ladder); a skill only appears on the phase tabs it has. Phase 2 = that skill's 0 exercises + its grade 2 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2334,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  PHASE 2 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -2571,7 +2569,7 @@
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  2 sets</t>
+          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  PHASE 2 of 3  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2782,7 @@
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  2 sets</t>
+          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  PHASE 2 of 3  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2973,7 @@
     <row r="41" ht="18.75" customHeight="1">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 2 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -3034,7 +3032,7 @@
     <row r="46" ht="18.75" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 2 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3171,7 @@
       </c>
       <c r="D53" s="9" t="inlineStr">
         <is>
-          <t>15–20 reps @ 20% BW</t>
+          <t>15–20 reps @ 10–20% BW</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3179,7 @@
     <row r="55" ht="18.75" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  2 sets</t>
+          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  PHASE 2 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3274,7 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ 20–30% BW</t>
+          <t>8–10 reps @ 15–30% BW</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3392,7 @@
     <row r="67" ht="18.75" customHeight="1">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  3 sets</t>
+          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  PHASE 2 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3487,7 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 45–50% BW</t>
+          <t>5–10 reps @ 40–45% BW</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3509,7 @@
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 12.5–15% BW</t>
+          <t>5–10 reps @ 10–12.5% BW</t>
         </is>
       </c>
     </row>
@@ -3519,7 +3517,7 @@
     <row r="75" ht="18.75" customHeight="1">
       <c r="A75" s="4" t="inlineStr">
         <is>
-          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  3 sets</t>
+          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  PHASE 2 of 3  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3642,7 @@
     <row r="83" ht="18.75" customHeight="1">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  3 sets</t>
+          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  PHASE 2 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3715,7 @@
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 15% BW</t>
+          <t>5–10 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3737,7 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 15% BW</t>
+          <t>5–10 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
@@ -3761,7 +3759,7 @@
       </c>
       <c r="D89" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 35–40% BW</t>
+          <t>5–10 reps @ 30–35% BW</t>
         </is>
       </c>
     </row>
@@ -3769,7 +3767,7 @@
     <row r="91" ht="18.75" customHeight="1">
       <c r="A91" s="4" t="inlineStr">
         <is>
-          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  3 sets</t>
+          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  PHASE 2 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3840,7 @@
       </c>
       <c r="D95" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ 10–15% BW</t>
+          <t>8–10 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
@@ -3850,7 +3848,7 @@
     <row r="97" ht="18.75" customHeight="1">
       <c r="A97" s="4" t="inlineStr">
         <is>
-          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  3 sets</t>
+          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  PHASE 2 of 4  ·  3 sets</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4009,7 @@
       </c>
       <c r="D105" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 45–50% BW</t>
+          <t>5–10 reps @ 40–45% BW</t>
         </is>
       </c>
     </row>
@@ -4033,7 +4031,7 @@
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 45–50% BW</t>
+          <t>5–10 reps @ 40–45% BW</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4053,7 @@
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 15–20% BW</t>
+          <t>5–10 reps @ 10–15% BW</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F127"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4285,10 +4283,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="40" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each block is one skill — train only the skill you are chasing. Phase 3 = the 0 exercises + the grade 3 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+          <t>Each block is one skill — train only the skill you are chasing. Skills have different numbers of phases (set by the grades on the skill ladder); a skill only appears on the phase tabs it has. Phase 3 = that skill's 0 exercises + its grade 3 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4311,7 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  PHASE 3 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -4479,259 +4477,259 @@
       </c>
     </row>
     <row r="14" ht="24" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Single arm plank hold</t>
+          <t>Supinated Shoulder Extension press</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>60s hold, hips in line with shoulders</t>
+          <t>15 reps arms straight with medium intensity band</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>30–60s</t>
+          <t>15 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Contra-lateral Bear Scapula pushups</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>10 push-ups each side + 30s hold each side</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps/side · rest · 10–30s hold/side</t>
+          <t>Full range iron cross press</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Single arm scapula pushups</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side, hips square</t>
-        </is>
-      </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Horizontal supinated support hold rings</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
+          <t>Rotational DB Push Hold</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>TBD</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Supinated Shoulder Extension press</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>15 reps arms straight with medium intensity band</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>15 reps · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Full range iron cross press</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+    <row r="17" ht="8" customHeight="1"/>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  PHASE 3 of 3  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
         </is>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Rotational DB Push Hold</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D20" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1"/>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  2 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
+          <t>Active Tuck Hang Hold</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>45s hold, knees in line with hips</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>20–45s</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Active Tuck Hang Reps</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>15 reps, knees in line with hips</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Contra-lateral retraction row + hold</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side + 30s hold each side</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps/side · rest · 10–30s hold/side</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Inverted Tuck Hang Scapula Retraction</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>10 reps</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Active Tuck Hang Hold</t>
+          <t>Cable Retraction</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>45s hold, knees in line with hips</t>
+          <t>15 reps at 30% bodyweight, each side</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>20–45s</t>
+          <t>10–15 reps @ 25–30% BW</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Active Tuck Hang Reps</t>
+          <t>Banded Pull Aparts</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>15 reps, knees in line with hips</t>
+          <t>15 reps medium resistance band</t>
         </is>
       </c>
       <c r="D25" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>15 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Contra-lateral retraction row + hold</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side + 30s hold each side</t>
-        </is>
-      </c>
-      <c r="D26" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps/side · rest · 10–30s hold/side</t>
+          <t>2 Arm Retraction Rows</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Inverted Tuck Hang Scapula Retraction</t>
+          <t>Banded Pulldowns</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>10 reps</t>
+          <t>20 reps with medium intensity band</t>
         </is>
       </c>
       <c r="D27" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4741,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Cable Retraction</t>
+          <t>DB Pull Hold</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -4765,142 +4763,142 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Banded Pull Aparts</t>
+          <t>Powell Raise</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>15 reps medium resistance band</t>
+          <t>12 reps each side 5% bodyweight</t>
         </is>
       </c>
       <c r="D29" s="9" t="inlineStr">
         <is>
-          <t>15 reps · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>2 Arm Retraction Rows</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Banded Pulldowns</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
-        <is>
-          <t>20 reps with medium intensity band</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>20 reps · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>DB Pull Hold</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="inlineStr">
-        <is>
-          <t>15 reps at 30% bodyweight, each side</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>10–15 reps @ 25–30% BW</t>
+          <t>12 reps each side @ 2.5–5% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="8" customHeight="1"/>
+    <row r="31" ht="18.75" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  PHASE 3 of 3  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
         </is>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Powell Raise</t>
+          <t>Inverted hang tuck to pencil leg lift</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>12 reps each side 5% bodyweight</t>
+          <t>12 reps, 2s hold each, neutral grip</t>
         </is>
       </c>
       <c r="D33" s="9" t="inlineStr">
         <is>
-          <t>12 reps each side @ 2.5–5% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="8" customHeight="1"/>
-    <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  2 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
+          <t>6–12 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Ring CARS</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Banded shoulder rotations</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each direction using a medium-intensity band</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>10 reps each direction · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>45 Degree German Hang</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>30s hold at ~45°</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>15–30s</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Inverted hang tuck to pencil leg lift</t>
+          <t>Extension dumbbell curls</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>12 reps, 2s hold each, neutral grip</t>
+          <t>15 reps at 10% bodyweight</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
         <is>
-          <t>6–12 reps</t>
+          <t>10–15 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
@@ -4912,17 +4910,17 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Ring CARS</t>
-        </is>
-      </c>
-      <c r="C38" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D38" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+          <t>Weighted Stick Shoulder Dislocates</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>10 reps of 5 lbs of added weight</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ stick only → 5 lb</t>
         </is>
       </c>
     </row>
@@ -4934,105 +4932,54 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Banded shoulder rotations</t>
+          <t>Weighted Shoulder Extension Pikes</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>10 reps each direction using a medium-intensity band</t>
+          <t>10 reps of 5 lbs added weight</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
         <is>
-          <t>10 reps each direction · light–medium resistance band</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>45 Degree German Hang</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>30s hold at ~45°</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>15–30s</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Extension dumbbell curls</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>15 reps at 10% bodyweight</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>10–15 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Weighted Stick Shoulder Dislocates</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>10 reps of 5 lbs of added weight</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
           <t>8–10 reps @ stick only → 5 lb</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="8" customHeight="1"/>
+    <row r="41" ht="18.75" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 3 of 4  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
         </is>
       </c>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Weighted Shoulder Extension Pikes</t>
+          <t>Feet Elevated Scissor Switches</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>10 reps of 5 lbs added weight</t>
+          <t>1 min hold, leg change every 2–3s</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ stick only → 5 lb</t>
+          <t>30–60s</t>
         </is>
       </c>
     </row>
@@ -5040,7 +4987,7 @@
     <row r="45" ht="18.75" customHeight="1">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  2 sets</t>
+          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 3 of 4  ·  2 sets</t>
         </is>
       </c>
     </row>
@@ -5059,208 +5006,208 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Feet Elevated Scissor Switches</t>
+          <t>P-bar Tuck Leg Raise</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>1 min hold, leg change every 2–3s</t>
+          <t>20 reps, knees to hip height</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
         <is>
+          <t>10–20 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Feet Assisted Pike Pull Through</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>10 reps</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Ring Dip Hold + Scapula Push downs Split Stance</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>20 scapula push downs · rest · 1 min hold, hips over shoulders</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="inlineStr">
+        <is>
+          <t>10–20 scap push downs · rest · 30–60s hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Hip flexion knee raise</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>25 reps on each leg</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>20–25 reps each leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Arms Up Tuck hollow body hold</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>60s hold</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
           <t>30–60s</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="24" customHeight="1">
-      <c r="A48" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Back to wall HS kick ups</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>5 reps each side, 3–5s wall hold</t>
-        </is>
-      </c>
-      <c r="D48" s="9" t="inlineStr">
-        <is>
-          <t>3–5 reps each side</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="24" customHeight="1">
-      <c r="A49" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>45 Degree Wall Handstand Hold</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
-        <is>
-          <t>1 min hold, arms straight</t>
-        </is>
-      </c>
-      <c r="D49" s="9" t="inlineStr">
-        <is>
-          <t>30–60s</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="8" customHeight="1"/>
-    <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  2 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Reverse cable squats</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>20 reps at 25% bodyweight</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>15–20 reps @ 20–25% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="8" customHeight="1"/>
+    <row r="54" ht="18.75" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  PHASE 3 of 4  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>◇  PICK 1  —  interchangeable, choose one</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="24" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
         <is>
           <t>○  3</t>
         </is>
       </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>P-bar Tuck Leg Raise</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>20 reps, knees to hip height</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>10–20 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="24" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Feet Assisted Pike Pull Through</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="inlineStr">
-        <is>
-          <t>10 reps</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="24" customHeight="1">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Ring Dip Hold + Scapula Push downs Split Stance</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>20 scapula push downs · rest · 1 min hold, hips over shoulders</t>
-        </is>
-      </c>
-      <c r="D55" s="9" t="inlineStr">
-        <is>
-          <t>10–20 scap push downs · rest · 30–60s hold</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="24" customHeight="1">
-      <c r="A56" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Ring Dip Hold + Scapula pushdowns Feet in Front</t>
+          <t>Active Tuck Hang Reps</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>20 scapula push downs · rest · 1 min hold</t>
+          <t>15 reps, knees in line with hips</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>10–20 scap push downs · rest · 30–60s hold</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Hip flexion knee raise</t>
+          <t>Active Tuck Hang Hold</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>25 reps on each leg</t>
+          <t>45s hold, knees in line with hips</t>
         </is>
       </c>
       <c r="D57" s="9" t="inlineStr">
         <is>
-          <t>20–25 reps each leg</t>
+          <t>20–45s</t>
         </is>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Arms Up Tuck hollow body hold</t>
+          <t>Inverted hang tuck to pencil leg lift</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>60s hold</t>
+          <t>12 reps, full inverted hang each rep</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>30–60s</t>
+          <t>6–12 reps</t>
         </is>
       </c>
     </row>
@@ -5272,230 +5219,230 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Reverse cable squats</t>
+          <t>1 Arm Cable Scapular Pulldown</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>20 reps at 25% bodyweight</t>
+          <t>10 reps at 40% bodyweight</t>
         </is>
       </c>
       <c r="D59" s="9" t="inlineStr">
         <is>
-          <t>15–20 reps @ 25% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="8" customHeight="1"/>
-    <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  2 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="15" customHeight="1">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
+          <t>8–10 reps @ 20–40% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>Overhead banded Pullaparts</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>20 reps with a medium resistance band</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>Banded Pull Aparts</t>
+        </is>
+      </c>
+      <c r="C61" s="8" t="inlineStr">
+        <is>
+          <t>15 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="inlineStr">
+        <is>
+          <t>15 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>Banded Pulldowns</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>20 reps with medium intensity band</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
     <row r="63" ht="24" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Active Tuck Hang Reps</t>
+          <t>Lateral Cable Pulldowns</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>15 reps, knees in line with hips</t>
+          <t>12 reps with 15% bodyweight</t>
         </is>
       </c>
       <c r="D63" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>12 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
     <row r="64" ht="24" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>DB Lat Pullover</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>12 reps with 15% bodyweight</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>12 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="8" customHeight="1"/>
+    <row r="66" ht="18.75" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  PHASE 3 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
           <t>○  3</t>
         </is>
       </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Active Tuck Hang Hold</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="inlineStr">
-        <is>
-          <t>45s hold, knees in line with hips</t>
-        </is>
-      </c>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>20–45s</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Inverted hang tuck to pencil leg lift</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="inlineStr">
-        <is>
-          <t>12 reps, full inverted hang each rep</t>
-        </is>
-      </c>
-      <c r="D65" s="9" t="inlineStr">
-        <is>
-          <t>6–12 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="24" customHeight="1">
-      <c r="A66" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Single arm assisted scapula pull-up</t>
-        </is>
-      </c>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>12 scapula pull downs each arm</t>
-        </is>
-      </c>
-      <c r="D66" s="9" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>Incline Ring Push-up</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>15 reps at a 45° angle</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
         <is>
           <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="24" customHeight="1">
-      <c r="A67" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Alternating Tuck L sit</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>45s hold (active hang)</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>20–45s</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="24" customHeight="1">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="inlineStr">
-        <is>
-          <t>Active Tuck to L Sit Eccentrics</t>
-        </is>
-      </c>
-      <c r="C68" s="8" t="inlineStr">
-        <is>
-          <t>10 reps, feet parallel to hips</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
         </is>
       </c>
     </row>
     <row r="69" ht="24" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>1 Arm Cable Scapular Pulldown</t>
+          <t>Eccentric push-up + kneeling concentric</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>10 reps at 40% bodyweight</t>
+          <t>15 reps</t>
         </is>
       </c>
       <c r="D69" s="9" t="inlineStr">
         <is>
-          <t>8–10 reps @ 30–40% BW</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
     <row r="70" ht="24" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Overhead banded Pullaparts</t>
+          <t>Single arm seated push-up</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>20 reps with a medium resistance band</t>
+          <t>10 reps each side</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>20 reps · light–medium resistance band</t>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
     <row r="71" ht="24" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>○  0</t>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Banded Pull Aparts</t>
+          <t>Bent arm push-up hold</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>15 reps medium resistance band</t>
+          <t>30s hold</t>
         </is>
       </c>
       <c r="D71" s="9" t="inlineStr">
         <is>
-          <t>15 reps · light–medium resistance band</t>
+          <t>15–30s</t>
         </is>
       </c>
     </row>
@@ -5507,17 +5454,17 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Banded Pulldowns</t>
+          <t>DB Push</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>20 reps with medium intensity band</t>
+          <t>10 reps at 60% bodyweight</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>20 reps · light–medium resistance band</t>
+          <t>5–10 reps @ 50–55% BW</t>
         </is>
       </c>
     </row>
@@ -5529,54 +5476,54 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Lateral Cable Pulldowns</t>
+          <t>Cable Chest Press</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>12 reps with 15% bodyweight</t>
+          <t>10 reps at 20% bodyweight</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
         <is>
-          <t>12 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="24" customHeight="1">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>DB Lat Pullover</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="inlineStr">
-        <is>
-          <t>12 reps with 15% bodyweight</t>
-        </is>
-      </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>12 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="8" customHeight="1"/>
-    <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  3 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1">
-      <c r="A77" s="5" t="inlineStr">
+          <t>5–10 reps @ 15–17.5% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="8" customHeight="1"/>
+    <row r="75" ht="18.75" customHeight="1">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  PHASE 3 of 3  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="24" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>Incline Bent Leg Single Arm Row</t>
+        </is>
+      </c>
+      <c r="C77" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each arm · body at a 45° angle, legs bent</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -5588,17 +5535,17 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Incline Ring Push-up</t>
+          <t>Ground Row Isometric Hold</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>15 reps at a 45° angle</t>
+          <t>30s hold at a horizontal angle</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>15–30s</t>
         </is>
       </c>
     </row>
@@ -5610,149 +5557,98 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Eccentric push-up + kneeling concentric</t>
+          <t>Ground Row</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>15 reps</t>
+          <t>12 reps</t>
         </is>
       </c>
       <c r="D79" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
+          <t>6–12 reps</t>
         </is>
       </c>
     </row>
     <row r="80" ht="24" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Single arm seated push-up</t>
+          <t>Single Arm DB Row</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>10 reps each side</t>
+          <t>10 reps at 35% bodyweight</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>5–10 reps @ 30–35% BW</t>
         </is>
       </c>
     </row>
     <row r="81" ht="24" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B81" s="7" t="inlineStr">
+        <is>
+          <t>Chest Supported DB Row</t>
+        </is>
+      </c>
+      <c r="C81" s="8" t="inlineStr">
+        <is>
+          <t>10 reps with 60% bodyweight (total, both hands)</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 55–60% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="8" customHeight="1"/>
+    <row r="83" ht="18.75" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  PHASE 3 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
           <t>○  3</t>
         </is>
       </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Bent arm push-up hold</t>
-        </is>
-      </c>
-      <c r="C81" s="8" t="inlineStr">
-        <is>
-          <t>30s hold</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
-        <is>
-          <t>15–30s</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="24" customHeight="1">
-      <c r="A82" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>2 Arm Pushup</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>15 reps</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="inlineStr">
-        <is>
-          <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="24" customHeight="1">
-      <c r="A83" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>2 Arm Rotational Pushup</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side</t>
-        </is>
-      </c>
-      <c r="D83" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="24" customHeight="1">
-      <c r="A84" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Rotational Lunge Push-up-two arms</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="24" customHeight="1">
-      <c r="A85" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>QDR Push-ups</t>
+          <t>Pike handstand pushup</t>
         </is>
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>10 reps, 2s hold each, knees off floor</t>
+          <t>12 reps</t>
         </is>
       </c>
       <c r="D85" s="9" t="inlineStr">
         <is>
-          <t>6–10 total reps  (3–5 each side)</t>
+          <t>5–12 reps</t>
         </is>
       </c>
     </row>
@@ -5764,17 +5660,17 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>DB Push</t>
+          <t>Seated Straddle 1 Arm OH Press</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>10 reps at 60% bodyweight</t>
+          <t>10 reps each arm at 20% bodyweight</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 55–60% BW</t>
+          <t>5–10 reps @ 15–20% BW</t>
         </is>
       </c>
     </row>
@@ -5786,54 +5682,54 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Cable Chest Press</t>
+          <t>Seated Bench Overhead Press</t>
         </is>
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>10 reps at 20% bodyweight</t>
+          <t>10 reps each side at 20% bodyweight</t>
         </is>
       </c>
       <c r="D87" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 17.5–20% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="8" customHeight="1"/>
-    <row r="89" ht="18.75" customHeight="1">
-      <c r="A89" s="4" t="inlineStr">
-        <is>
-          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  3 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="15" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
+          <t>5–10 reps @ 15–20% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="24" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>BB Overhead Press</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 50% bodyweight</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 40–45% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="8" customHeight="1"/>
+    <row r="90" ht="18.75" customHeight="1">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  PHASE 3 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>◇  PICK 1  —  interchangeable, choose one</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="24" customHeight="1">
-      <c r="A91" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Incline Bent Leg Single Arm Row</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each arm · body at a 45° angle, legs bent</t>
-        </is>
-      </c>
-      <c r="D91" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -5845,17 +5741,17 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Ground Row Isometric Hold</t>
+          <t>2 Arm Ring Dip, Split Stance</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>30s hold at a horizontal angle</t>
+          <t>15 reps, 90°+ shoulder bend</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>15–30s</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
@@ -5867,17 +5763,17 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Ground Row</t>
+          <t>Feet Behind Dips</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>12 reps</t>
+          <t>15 reps, minimal weight on feet</t>
         </is>
       </c>
       <c r="D93" s="9" t="inlineStr">
         <is>
-          <t>6–12 reps</t>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
@@ -5889,54 +5785,54 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Single Arm DB Row</t>
+          <t>1 Arm Cable Dip</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>10 reps at 35% bodyweight</t>
+          <t>10 reps at 20% bodyweight</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 30–35% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="24" customHeight="1">
-      <c r="A95" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Chest Supported DB Row</t>
-        </is>
-      </c>
-      <c r="C95" s="8" t="inlineStr">
-        <is>
-          <t>10 reps with 60% bodyweight (total, both hands)</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 55–60% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="8" customHeight="1"/>
-    <row r="97" ht="18.75" customHeight="1">
-      <c r="A97" s="4" t="inlineStr">
-        <is>
-          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  3 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1">
-      <c r="A98" s="5" t="inlineStr">
+          <t>8–10 reps @ 10–20% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="8" customHeight="1"/>
+    <row r="96" ht="18.75" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  PHASE 3 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
+        </is>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>Assisted L-sit chin-up</t>
+        </is>
+      </c>
+      <c r="C98" s="8" t="inlineStr">
+        <is>
+          <t>10 reps, chin over rings</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
         </is>
       </c>
     </row>
@@ -5948,39 +5844,39 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Pike handstand pushup</t>
+          <t>Band Chinup</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>12 reps</t>
+          <t>10 reps, lightest band</t>
         </is>
       </c>
       <c r="D99" s="9" t="inlineStr">
         <is>
-          <t>5–12 reps</t>
+          <t>6–10 reps · medium → light band</t>
         </is>
       </c>
     </row>
     <row r="100" ht="24" customHeight="1">
-      <c r="A100" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>○  3</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Eccentric Feet Elevated Pike Pushup</t>
+          <t>Band Pullup</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>10 reps, 3s eccentric lowering</t>
+          <t>10 reps, lightest band</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>6–10 reps</t>
+          <t>6–10 reps · medium → light band</t>
         </is>
       </c>
     </row>
@@ -5992,17 +5888,17 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Seated Straddle 1 Arm OH Press</t>
-        </is>
-      </c>
-      <c r="C101" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each arm at 20% bodyweight</t>
-        </is>
-      </c>
-      <c r="D101" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 20% BW</t>
+          <t>Weighted stick elbow rotations</t>
+        </is>
+      </c>
+      <c r="C101" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -6014,17 +5910,17 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Seated Bench Overhead Press</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t>10 reps each side at 20% bodyweight</t>
-        </is>
-      </c>
-      <c r="D102" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 20% BW</t>
+          <t>Banded Lat Pullover</t>
+        </is>
+      </c>
+      <c r="C102" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
         </is>
       </c>
     </row>
@@ -6036,564 +5932,206 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>BB Overhead Press</t>
+          <t>DB bicep curl</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>10 reps at 50% bodyweight</t>
+          <t>15 reps 15% of bodyweight</t>
         </is>
       </c>
       <c r="D103" s="9" t="inlineStr">
         <is>
-          <t>5–10 reps @ 45–50% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="8" customHeight="1"/>
-    <row r="105" ht="18.75" customHeight="1">
-      <c r="A105" s="4" t="inlineStr">
-        <is>
-          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  3 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
+          <t>15 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>Latpulldown- Chinup</t>
+        </is>
+      </c>
+      <c r="C104" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 60% bodyweight</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 50–55% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Latpulldown- Pull-up</t>
+        </is>
+      </c>
+      <c r="C105" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 60% bodyweight</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 50–55% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>1 Arm Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 30% bodyweight</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 20–25% BW</t>
         </is>
       </c>
     </row>
     <row r="107" ht="24" customHeight="1">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>○  3</t>
+          <t>○  0</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>2 Arm Ring Dip, Split Stance</t>
+          <t>DB Lat Pullover</t>
         </is>
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>15 reps, 90°+ shoulder bend</t>
+          <t>12 reps with 15% bodyweight</t>
         </is>
       </c>
       <c r="D107" s="9" t="inlineStr">
         <is>
-          <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="24" customHeight="1">
-      <c r="A108" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>Feet Behind Dips</t>
-        </is>
-      </c>
-      <c r="C108" s="8" t="inlineStr">
-        <is>
-          <t>15 reps, minimal weight on feet</t>
-        </is>
-      </c>
-      <c r="D108" s="9" t="inlineStr">
-        <is>
-          <t>5–15 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="inlineStr">
-        <is>
-          <t>Bottom Of Dip Hold Feet off the Ground</t>
-        </is>
-      </c>
-      <c r="C109" s="8" t="inlineStr">
-        <is>
-          <t>20s hold past 90°</t>
-        </is>
-      </c>
-      <c r="D109" s="9" t="inlineStr">
-        <is>
-          <t>10–20s</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="24" customHeight="1">
-      <c r="A110" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="inlineStr">
-        <is>
-          <t>Banded Dips</t>
-        </is>
-      </c>
-      <c r="C110" s="8" t="inlineStr">
-        <is>
-          <t>15 reps, lightest band</t>
-        </is>
-      </c>
-      <c r="D110" s="9" t="inlineStr">
-        <is>
-          <t>5–15 reps · medium → light band</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="24" customHeight="1">
-      <c r="A111" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="inlineStr">
-        <is>
-          <t>Eccentric Dips</t>
-        </is>
-      </c>
-      <c r="C111" s="8" t="inlineStr">
-        <is>
-          <t>10 eccentric reps, 1s hold bottom</t>
-        </is>
-      </c>
-      <c r="D111" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="24" customHeight="1">
-      <c r="A112" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>1 Arm Cable Dip</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 20% bodyweight</t>
-        </is>
-      </c>
-      <c r="D112" s="9" t="inlineStr">
-        <is>
-          <t>8–10 reps @ 15–20% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="8" customHeight="1"/>
-    <row r="114" ht="18.75" customHeight="1">
-      <c r="A114" s="4" t="inlineStr">
-        <is>
-          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  3 sets</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="5" t="inlineStr">
-        <is>
-          <t>◇  PICK 1  —  interchangeable, choose one</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="24" customHeight="1">
-      <c r="A116" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="inlineStr">
-        <is>
-          <t>Assisted L-sit chin-up</t>
-        </is>
-      </c>
-      <c r="C116" s="8" t="inlineStr">
-        <is>
-          <t>10 reps, chin over rings</t>
-        </is>
-      </c>
-      <c r="D116" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="24" customHeight="1">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="inlineStr">
-        <is>
-          <t>Band Chinup</t>
-        </is>
-      </c>
-      <c r="C117" s="8" t="inlineStr">
-        <is>
-          <t>10 reps, lightest band</t>
-        </is>
-      </c>
-      <c r="D117" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps · medium → light band</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>○  3</t>
-        </is>
-      </c>
-      <c r="B118" s="7" t="inlineStr">
-        <is>
-          <t>Band Pullup</t>
-        </is>
-      </c>
-      <c r="C118" s="8" t="inlineStr">
-        <is>
-          <t>10 reps, lightest band</t>
-        </is>
-      </c>
-      <c r="D118" s="9" t="inlineStr">
-        <is>
-          <t>6–10 reps · medium → light band</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="24" customHeight="1">
-      <c r="A119" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B119" s="7" t="inlineStr">
-        <is>
-          <t>Eccentric Chinup</t>
-        </is>
-      </c>
-      <c r="C119" s="8" t="inlineStr">
-        <is>
-          <t>8 reps · 3s eccentric with control into passive hang</t>
-        </is>
-      </c>
-      <c r="D119" s="9" t="inlineStr">
-        <is>
-          <t>4–8 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="24" customHeight="1">
-      <c r="A120" s="12" t="inlineStr">
-        <is>
-          <t>○  4</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Eccentric Pullup</t>
-        </is>
-      </c>
-      <c r="C120" s="8" t="inlineStr">
-        <is>
-          <t>8 reps · 3s eccentric with control into passive hang</t>
-        </is>
-      </c>
-      <c r="D120" s="9" t="inlineStr">
-        <is>
-          <t>4–8 reps</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="24" customHeight="1">
-      <c r="A121" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="inlineStr">
-        <is>
-          <t>Weighted stick elbow rotations</t>
-        </is>
-      </c>
-      <c r="C121" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D121" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="24" customHeight="1">
-      <c r="A122" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>Banded Lat Pullover</t>
-        </is>
-      </c>
-      <c r="C122" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D122" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-    </row>
-    <row r="123" ht="24" customHeight="1">
-      <c r="A123" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>DB bicep curl</t>
-        </is>
-      </c>
-      <c r="C123" s="8" t="inlineStr">
-        <is>
-          <t>15 reps 15% of bodyweight</t>
-        </is>
-      </c>
-      <c r="D123" s="9" t="inlineStr">
-        <is>
-          <t>15 reps @ 5–15% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="24" customHeight="1">
-      <c r="A124" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>Latpulldown- Chinup</t>
-        </is>
-      </c>
-      <c r="C124" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 60% bodyweight</t>
-        </is>
-      </c>
-      <c r="D124" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 55–60% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="125" ht="24" customHeight="1">
-      <c r="A125" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>Latpulldown- Pull-up</t>
-        </is>
-      </c>
-      <c r="C125" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 60% bodyweight</t>
-        </is>
-      </c>
-      <c r="D125" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 55–60% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="126" ht="24" customHeight="1">
-      <c r="A126" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="inlineStr">
-        <is>
-          <t>1 Arm Lat Pulldown</t>
-        </is>
-      </c>
-      <c r="C126" s="8" t="inlineStr">
-        <is>
-          <t>10 reps at 30% bodyweight</t>
-        </is>
-      </c>
-      <c r="D126" s="9" t="inlineStr">
-        <is>
-          <t>5–10 reps @ 25–30% BW</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="24" customHeight="1">
-      <c r="A127" s="6" t="inlineStr">
-        <is>
-          <t>○  0</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="inlineStr">
-        <is>
-          <t>DB Lat Pullover</t>
-        </is>
-      </c>
-      <c r="C127" s="8" t="inlineStr">
-        <is>
-          <t>12 reps with 15% bodyweight</t>
-        </is>
-      </c>
-      <c r="D127" s="9" t="inlineStr">
-        <is>
           <t>12 reps @ 5–15% BW</t>
         </is>
       </c>
     </row>
-    <row r="128" ht="8" customHeight="1"/>
+    <row r="108" ht="8" customHeight="1"/>
   </sheetData>
-  <mergeCells count="116">
+  <mergeCells count="96">
     <mergeCell ref="D11:F11"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A75:F75"/>
     <mergeCell ref="D47:F47"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="D28:F28"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D102:F102"/>
     <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A32:F32"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="A97:F97"/>
     <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D30:F30"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D23:F23"/>
     <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D105:F105"/>
     <mergeCell ref="D57:F57"/>
+    <mergeCell ref="A41:F41"/>
     <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D41:F41"/>
     <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="A18:F18"/>
     <mergeCell ref="D43:F43"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="D106:F106"/>
     <mergeCell ref="D93:F93"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A62:F62"/>
     <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D83:F83"/>
     <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D110:F110"/>
     <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D60:F60"/>
     <mergeCell ref="D69:F69"/>
     <mergeCell ref="D100:F100"/>
-    <mergeCell ref="A114:F114"/>
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D21:F21"/>
     <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="D104:F104"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A90:F90"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="A105:F105"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D78:F78"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D87:F87"/>
     <mergeCell ref="A76:F76"/>
-    <mergeCell ref="D122:F122"/>
     <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D18:F18"/>
     <mergeCell ref="D58:F58"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D121:F121"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="A83:F83"/>
     <mergeCell ref="D59:F59"/>
     <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D34:F34"/>
     <mergeCell ref="D99:F99"/>
-    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A45:F45"/>
-    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D36:F36"/>
     <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D77:F77"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D61:F61"/>
     <mergeCell ref="D70:F70"/>
-    <mergeCell ref="A89:F89"/>
     <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D125:F125"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D112:F112"/>
     <mergeCell ref="D4:F4"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D62:F62"/>
     <mergeCell ref="D56:F56"/>
-    <mergeCell ref="A106:F106"/>
-    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="A91:F91"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="D64:F64"/>
     <mergeCell ref="D38:F38"/>
-    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="D98:F98"/>
     <mergeCell ref="D79:F79"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="D88:F88"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A77:F77"/>
     <mergeCell ref="D63:F63"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D65:F65"/>
     <mergeCell ref="A6:F6"/>
+    <mergeCell ref="D52:F52"/>
     <mergeCell ref="D49:F49"/>
   </mergeCells>
   <hyperlinks>
@@ -6607,87 +6145,67 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B15" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B19" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B26" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B54" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B55" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B47" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B48" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B49" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B56" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B61" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B62" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B63" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B74" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B82" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B83" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B84" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B91" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B95" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B108" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B109" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B110" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B123" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B124" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B125" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B126" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B127" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B73" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B77" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B78" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B79" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B80" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B81" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B85" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B86" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B87" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B88" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B92" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B93" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B94" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B98" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B99" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B100" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B101" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B102" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B103" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B104" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B105" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B106" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B107" r:id="rId71"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6695,6 +6213,1284 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="8.710000000000001" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="31.5" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TRAIN A SKILL — UPPER BODY STRENGTH  ·  LEVEL 1  ·  PHASE 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="40" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each block is one skill — train only the skill you are chasing. Skills have different numbers of phases (set by the grades on the skill ladder); a skill only appears on the phase tabs it has. Phase 4 = that skill's 0 exercises + its grade 4 exercises. Self-paced — stay on each exercise until the standard is earned; train inside the PRESCRIPTION range, the top of the range is the STANDARD. ◇ PICK 1 = choose one. Every cell is a per-set prescription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="21.75" customHeight="1">
+      <c r="A4" s="3" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>EXERCISE</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>STANDARD</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>PRESCRIPTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  PHASE 4 of 4  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Single arm plank hold</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>60s hold, hips in line with shoulders</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>30–60s</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Contra-lateral Bear Scapula pushups</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>10 push-ups each side + 30s hold each side</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps/side · rest · 10–30s hold/side</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Single arm scapula pushups</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side, hips square</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Horizontal supinated support hold rings</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Supinated Shoulder Extension press</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>15 reps arms straight with medium intensity band</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>15 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Full range iron cross press</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Rotational DB Push Hold</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="8" customHeight="1"/>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 4 of 4  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Back to wall HS kick ups</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>5 reps each side, 3–5s wall hold</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>3–5 reps each side</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>45 Degree Wall Handstand Hold</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>1 min hold, arms straight</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>30–60s</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="18.75" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  PHASE 4 of 4  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Ring Dip Hold + Scapula pushdowns Feet in Front</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>20 scapula push downs · rest · 1 min hold</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>10–20 scap push downs · rest · 30–60s hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Hip flexion knee raise</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>25 reps on each leg</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>20–25 reps each leg</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Arms Up Tuck hollow body hold</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>60s hold</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>30–60s</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Reverse cable squats</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>20 reps at 25% bodyweight</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>15–20 reps @ 25% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="8" customHeight="1"/>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  PHASE 4 of 4  ·  2 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Single arm assisted scapula pull-up</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>12 scapula pull downs each arm</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Alternating Tuck L sit</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>45s hold (active hang)</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>20–45s</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Active Tuck to L Sit Eccentrics</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>10 reps, feet parallel to hips</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1 Arm Cable Scapular Pulldown</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 40% bodyweight</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ 30–40% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Overhead banded Pullaparts</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>20 reps with a medium resistance band</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Banded Pull Aparts</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>15 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>15 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Banded Pulldowns</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>20 reps with medium intensity band</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Lateral Cable Pulldowns</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>12 reps with 15% bodyweight</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>12 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>DB Lat Pullover</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>12 reps with 15% bodyweight</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>12 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="8" customHeight="1"/>
+    <row r="39" ht="18.75" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  PHASE 4 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>2 Arm Pushup</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>15 reps</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>2 Arm Rotational Pushup</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Rotational Lunge Push-up-two arms</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="24" customHeight="1">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>QDR Push-ups</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>10 reps, 2s hold each, knees off floor</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>6–10 total reps  (3–5 each side)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>DB Push</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 60% bodyweight</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 55–60% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Cable Chest Press</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 20% bodyweight</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 17.5–20% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="8" customHeight="1"/>
+    <row r="48" ht="18.75" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  PHASE 4 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>Eccentric Feet Elevated Pike Pushup</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>10 reps, 3s eccentric lowering</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>Seated Straddle 1 Arm OH Press</t>
+        </is>
+      </c>
+      <c r="C51" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each arm at 20% bodyweight</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 20% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>Seated Bench Overhead Press</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>10 reps each side at 20% bodyweight</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 20% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>BB Overhead Press</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 50% bodyweight</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 45–50% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="8" customHeight="1"/>
+    <row r="55" ht="18.75" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  PHASE 4 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>Bottom Of Dip Hold Feet off the Ground</t>
+        </is>
+      </c>
+      <c r="C57" s="8" t="inlineStr">
+        <is>
+          <t>20s hold past 90°</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="inlineStr">
+        <is>
+          <t>10–20s</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>Banded Dips</t>
+        </is>
+      </c>
+      <c r="C58" s="8" t="inlineStr">
+        <is>
+          <t>15 reps, lightest band</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps · medium → light band</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>Eccentric Dips</t>
+        </is>
+      </c>
+      <c r="C59" s="8" t="inlineStr">
+        <is>
+          <t>10 eccentric reps, 1s hold bottom</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="inlineStr">
+        <is>
+          <t>6–10 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1 Arm Cable Dip</t>
+        </is>
+      </c>
+      <c r="C60" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 20% bodyweight</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>8–10 reps @ 15–20% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="8" customHeight="1"/>
+    <row r="62" ht="18.75" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  PHASE 4 of 4  ·  3 sets</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>◇  PICK 1  —  interchangeable, choose one</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>Eccentric Chinup</t>
+        </is>
+      </c>
+      <c r="C64" s="8" t="inlineStr">
+        <is>
+          <t>8 reps · 3s eccentric with control into passive hang</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>4–8 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>○  4</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>Eccentric Pullup</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>8 reps · 3s eccentric with control into passive hang</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>4–8 reps</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="24" customHeight="1">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>Weighted stick elbow rotations</t>
+        </is>
+      </c>
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Banded Lat Pullover</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>DB bicep curl</t>
+        </is>
+      </c>
+      <c r="C68" s="8" t="inlineStr">
+        <is>
+          <t>15 reps 15% of bodyweight</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>15 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>Latpulldown- Chinup</t>
+        </is>
+      </c>
+      <c r="C69" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 60% bodyweight</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 55–60% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>Latpulldown- Pull-up</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 60% bodyweight</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 55–60% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1 Arm Lat Pulldown</t>
+        </is>
+      </c>
+      <c r="C71" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 30% bodyweight</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>5–10 reps @ 25–30% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>○  0</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>DB Lat Pullover</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>12 reps with 15% bodyweight</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>12 reps @ 5–15% BW</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="8" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="64">
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D57:F57"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B12" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B17" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B18" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B22" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B23" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B24" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B25" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B29" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B30" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B31" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B32" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B50" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B51" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B52" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B53" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B57" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B58" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B59" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B60" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B64" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B65" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B66" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B67" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B68" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B69" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B70" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B71" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B72" r:id="rId45"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6721,7 +7517,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each block is one skill's TEST. Train inside the PRESCRIPTION range; the top of the range is the TEST standard (✦). Hit the standard once to pass, film it, submit to Skool.</t>
+          <t>Each block is one skill's TEST, taken after that skill's last phase. Train inside the PRESCRIPTION range; the top of the range is the TEST standard (✦). Hit the standard once to pass, film it, submit to Skool.</t>
         </is>
       </c>
     </row>
@@ -6746,27 +7542,27 @@
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  TEST · 2 sets</t>
+          <t>CONTRA-LATERAL PLANK HOLD  ·  HORIZONTAL STRAIGHT ARM PUSH  ·  TEST after Phase 4  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>TEST: Contra-lateral Plank Hold</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="14" t="inlineStr">
         <is>
           <t>PASS: 30s hold each side</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="15" t="inlineStr">
         <is>
           <t>10–30s each side · 2 sets</t>
         </is>
@@ -6776,27 +7572,27 @@
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  TEST · 2 sets</t>
+          <t>ARCHING HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  TEST after Phase 3  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>TEST: Arching Hang Hold</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>PASS: 30s unbroken arching hang</t>
         </is>
       </c>
-      <c r="D9" s="16" t="inlineStr">
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t>10–30s · 2 sets</t>
         </is>
@@ -6806,27 +7602,27 @@
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  TEST · 2 sets</t>
+          <t>GERMAN HANG HOLD  ·  HORIZONTAL STRAIGHT ARM PULL  ·  TEST after Phase 3  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>TEST: German Hang Hold Feet On Ground</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>PASS: 30s german hang (feet on ground)</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="D12" s="15" t="inlineStr">
         <is>
           <t>10–30s · 2 sets</t>
         </is>
@@ -6836,27 +7632,27 @@
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  TEST · 2 sets</t>
+          <t>CHEST TO WALL HANDSTAND HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  TEST after Phase 4  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>TEST: Chest to Wall Handstand Hold</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>PASS: 1 minute hold</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>20–60s · 2 sets  ✦</t>
         </is>
@@ -6866,27 +7662,27 @@
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  TEST · 2 sets</t>
+          <t>TUCK SUPPORT HOLD  ·  VERTICAL STRAIGHT ARM PUSH  ·  TEST after Phase 4  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>TEST: Tuck Support Hold- High bar</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>PASS: 30 second hold</t>
         </is>
       </c>
-      <c r="D18" s="16" t="inlineStr">
+      <c r="D18" s="15" t="inlineStr">
         <is>
           <t>10–30s · 2 sets  ✦</t>
         </is>
@@ -6896,27 +7692,27 @@
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  TEST · 2 sets</t>
+          <t>HANGING L SIT  ·  VERTICAL STRAIGHT ARM PULL  ·  TEST after Phase 4  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>TEST: Hanging L Sit</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr">
         <is>
           <t>PASS: 30 second hold</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr">
+      <c r="D21" s="15" t="inlineStr">
         <is>
           <t>10–30s · 2 sets  ✦</t>
         </is>
@@ -6926,49 +7722,49 @@
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  TEST · 2 sets  (Type 3 — one line unlocks two skills)</t>
+          <t>HIGH LIZARD CRAWL WITH PUSH-UP  ·  HORIZONTAL BENT ARM PUSH  ·  TEST after Phase 4  ·  2 sets  (Type 3 — one line unlocks two skills)</t>
         </is>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>TEST: High Lizard Crawl-with push-up</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr">
         <is>
           <t>PASS: 12 reps full range</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr">
+      <c r="D24" s="15" t="inlineStr">
         <is>
           <t>6–12 reps · 2 sets</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>TEST: Rotational High Lizard Crawl-with push-up</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>PASS: 12 reps full range</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr">
+      <c r="D25" s="15" t="inlineStr">
         <is>
           <t>6–12 reps · 2 sets</t>
         </is>
@@ -6978,27 +7774,27 @@
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  TEST · 2 sets</t>
+          <t>RING PULL: 2 ARM FEET ELEVATED  ·  HORIZONTAL BENT ARM PULL  ·  TEST after Phase 3  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>TEST: Ring Pull: 2 Arm Feet Elevated</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="14" t="inlineStr">
         <is>
           <t>PASS: 10 reps feet elevated</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr">
+      <c r="D28" s="15" t="inlineStr">
         <is>
           <t>4–10 reps · 2 sets</t>
         </is>
@@ -7008,27 +7804,27 @@
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  TEST · 2 sets</t>
+          <t>PIKE ELEVATED HSPU  ·  VERTICAL BENT ARM PUSH  ·  TEST after Phase 4  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>TEST: Pike Elevated HSPU</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>PASS: 10 reps</t>
         </is>
       </c>
-      <c r="D31" s="16" t="inlineStr">
+      <c r="D31" s="15" t="inlineStr">
         <is>
           <t>4–10 reps · 2 sets  ✦</t>
         </is>
@@ -7038,27 +7834,27 @@
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  TEST · 2 sets</t>
+          <t>2 ARM DIP  ·  VERTICAL BENT ARM PUSH  ·  TEST after Phase 4  ·  2 sets</t>
         </is>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="13" t="inlineStr">
         <is>
           <t>TEST: Box/ Bar Push: 2 Arm Dip</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="14" t="inlineStr">
         <is>
           <t>PASS: 10 reps past 90°</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="15" t="inlineStr">
         <is>
           <t>4–10 reps past 90° · 2 sets  ✦</t>
         </is>
@@ -7068,49 +7864,49 @@
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  TEST · 2 sets  (both required)</t>
+          <t>CHIN-UP + PULL-UP  ·  VERTICAL BENT ARM PULL  ·  TEST after Phase 4  ·  2 sets  (both required)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="13" t="inlineStr">
         <is>
           <t>TEST: Ring/ Bar Chinup</t>
         </is>
       </c>
-      <c r="C37" s="15" t="inlineStr">
+      <c r="C37" s="14" t="inlineStr">
         <is>
           <t>PASS: 5 reps</t>
         </is>
       </c>
-      <c r="D37" s="16" t="inlineStr">
+      <c r="D37" s="15" t="inlineStr">
         <is>
           <t>1–5 reps · 2 sets  ✦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="12" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="13" t="inlineStr">
         <is>
           <t>TEST: Ring/ Bar Pullups</t>
         </is>
       </c>
-      <c r="C38" s="15" t="inlineStr">
+      <c r="C38" s="14" t="inlineStr">
         <is>
           <t>PASS: 5 reps</t>
         </is>
       </c>
-      <c r="D38" s="16" t="inlineStr">
+      <c r="D38" s="15" t="inlineStr">
         <is>
           <t>1–5 reps · 2 sets  ✦</t>
         </is>

--- a/Train_A_Skill/Level1_Train_A_Skill.xlsx
+++ b/Train_A_Skill/Level1_Train_A_Skill.xlsx
@@ -751,14 +751,14 @@
           <t>Full range iron cross press</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 5% of body weight</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5% BW</t>
         </is>
       </c>
     </row>
@@ -2532,14 +2532,14 @@
           <t>Full range iron cross press</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 5% of body weight</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5% BW</t>
         </is>
       </c>
     </row>
@@ -4509,14 +4509,14 @@
           <t>Full range iron cross press</t>
         </is>
       </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 5% of body weight</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5% BW</t>
         </is>
       </c>
     </row>
@@ -6396,14 +6396,14 @@
           <t>Full range iron cross press</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>10 reps at 5% of body weight</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5% BW</t>
         </is>
       </c>
     </row>

--- a/Train_A_Skill/Level1_Train_A_Skill.xlsx
+++ b/Train_A_Skill/Level1_Train_A_Skill.xlsx
@@ -94,7 +94,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -118,11 +118,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE599"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFEAF6E1"/>
       </patternFill>
     </fill>
@@ -139,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -168,22 +163,16 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -773,14 +762,14 @@
           <t>Rotational DB Push Hold</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>30% of bodyweight for 15 reps</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>10–15 reps @ 5–10% BW</t>
         </is>
       </c>
     </row>
@@ -898,14 +887,14 @@
           <t>2 Arm Retraction Rows</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>20 reps at horizontal angle</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>10–20 reps</t>
         </is>
       </c>
     </row>
@@ -1023,14 +1012,14 @@
           <t>Ring CARS</t>
         </is>
       </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>15 reps</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
@@ -1979,14 +1968,14 @@
           <t>Weighted stick elbow rotations</t>
         </is>
       </c>
-      <c r="C92" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D92" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C92" s="8" t="inlineStr">
+        <is>
+          <t>5lb weighted bar for 10 reps</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5 lb</t>
         </is>
       </c>
     </row>
@@ -2001,14 +1990,14 @@
           <t>Banded Lat Pullover</t>
         </is>
       </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C93" s="8" t="inlineStr">
+        <is>
+          <t>20 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -2554,14 +2543,14 @@
           <t>Rotational DB Push Hold</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>30% of bodyweight for 15 reps</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>10–15 reps @ 10–15% BW</t>
         </is>
       </c>
     </row>
@@ -2701,14 +2690,14 @@
           <t>2 Arm Retraction Rows</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>20 reps at horizontal angle</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>10–20 reps</t>
         </is>
       </c>
     </row>
@@ -2848,14 +2837,14 @@
           <t>Ring CARS</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>15 reps</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
@@ -3936,14 +3925,14 @@
           <t>Weighted stick elbow rotations</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>5lb weighted bar for 10 reps</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5 lb</t>
         </is>
       </c>
     </row>
@@ -3958,14 +3947,14 @@
           <t>Banded Lat Pullover</t>
         </is>
       </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D103" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C103" s="8" t="inlineStr">
+        <is>
+          <t>20 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -4531,14 +4520,14 @@
           <t>Rotational DB Push Hold</t>
         </is>
       </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>30% of bodyweight for 15 reps</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>10–15 reps @ 20–25% BW</t>
         </is>
       </c>
     </row>
@@ -4700,14 +4689,14 @@
           <t>2 Arm Retraction Rows</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>20 reps at horizontal angle</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>10–20 reps</t>
         </is>
       </c>
     </row>
@@ -4825,14 +4814,14 @@
           <t>Ring CARS</t>
         </is>
       </c>
-      <c r="C34" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>15 reps</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>5–15 reps</t>
         </is>
       </c>
     </row>
@@ -5891,14 +5880,14 @@
           <t>Weighted stick elbow rotations</t>
         </is>
       </c>
-      <c r="C101" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D101" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C101" s="8" t="inlineStr">
+        <is>
+          <t>5lb weighted bar for 10 reps</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5 lb</t>
         </is>
       </c>
     </row>
@@ -5913,14 +5902,14 @@
           <t>Banded Lat Pullover</t>
         </is>
       </c>
-      <c r="C102" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D102" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C102" s="8" t="inlineStr">
+        <is>
+          <t>20 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -6352,14 +6341,14 @@
           <t>Horizontal supinated support hold rings</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>45s hold fully horizontal scapula in protraction</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>20–45s</t>
         </is>
       </c>
     </row>
@@ -6418,14 +6407,14 @@
           <t>Rotational DB Push Hold</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>30% of bodyweight for 15 reps</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>10–15 reps @ 25–30% BW</t>
         </is>
       </c>
     </row>
@@ -7227,14 +7216,14 @@
           <t>Weighted stick elbow rotations</t>
         </is>
       </c>
-      <c r="C66" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C66" s="8" t="inlineStr">
+        <is>
+          <t>5lb weighted bar for 10 reps</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>10 reps @ 2.5–5 lb</t>
         </is>
       </c>
     </row>
@@ -7249,14 +7238,14 @@
           <t>Banded Lat Pullover</t>
         </is>
       </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>TBD</t>
-        </is>
-      </c>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>TBD</t>
+      <c r="C67" s="8" t="inlineStr">
+        <is>
+          <t>20 reps medium resistance band</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>20 reps · light–medium resistance band</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7536,22 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>TEST: Contra-lateral Plank Hold</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>PASS: 30s hold each side</t>
         </is>
       </c>
-      <c r="D6" s="15" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>10–30s each side · 2 sets</t>
         </is>
@@ -7577,22 +7566,22 @@
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>TEST: Arching Hang Hold</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>PASS: 30s unbroken arching hang</t>
         </is>
       </c>
-      <c r="D9" s="15" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>10–30s · 2 sets</t>
         </is>
@@ -7607,22 +7596,22 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>TEST: German Hang Hold Feet On Ground</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>PASS: 30s german hang (feet on ground)</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>10–30s · 2 sets</t>
         </is>
@@ -7637,22 +7626,22 @@
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>TEST: Chest to Wall Handstand Hold</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>PASS: 1 minute hold</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>20–60s · 2 sets  ✦</t>
         </is>
@@ -7667,22 +7656,22 @@
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>TEST: Tuck Support Hold- High bar</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>PASS: 30 second hold</t>
         </is>
       </c>
-      <c r="D18" s="15" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>10–30s · 2 sets  ✦</t>
         </is>
@@ -7697,22 +7686,22 @@
       </c>
     </row>
     <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>TEST: Hanging L Sit</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>PASS: 30 second hold</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>10–30s · 2 sets  ✦</t>
         </is>
@@ -7727,44 +7716,44 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>TEST: High Lizard Crawl-with push-up</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>PASS: 12 reps full range</t>
         </is>
       </c>
-      <c r="D24" s="15" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>6–12 reps · 2 sets</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
         <is>
           <t>TEST: Rotational High Lizard Crawl-with push-up</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>PASS: 12 reps full range</t>
         </is>
       </c>
-      <c r="D25" s="15" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
         <is>
           <t>6–12 reps · 2 sets</t>
         </is>
@@ -7779,22 +7768,22 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B28" s="13" t="inlineStr">
+      <c r="B28" s="11" t="inlineStr">
         <is>
           <t>TEST: Ring Pull: 2 Arm Feet Elevated</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>PASS: 10 reps feet elevated</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
+      <c r="D28" s="13" t="inlineStr">
         <is>
           <t>4–10 reps · 2 sets</t>
         </is>
@@ -7809,22 +7798,22 @@
       </c>
     </row>
     <row r="31" ht="24" customHeight="1">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B31" s="13" t="inlineStr">
+      <c r="B31" s="11" t="inlineStr">
         <is>
           <t>TEST: Pike Elevated HSPU</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>PASS: 10 reps</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>4–10 reps · 2 sets  ✦</t>
         </is>
@@ -7839,22 +7828,22 @@
       </c>
     </row>
     <row r="34" ht="24" customHeight="1">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
         <is>
           <t>TEST: Box/ Bar Push: 2 Arm Dip</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="12" t="inlineStr">
         <is>
           <t>PASS: 10 reps past 90°</t>
         </is>
       </c>
-      <c r="D34" s="15" t="inlineStr">
+      <c r="D34" s="13" t="inlineStr">
         <is>
           <t>4–10 reps past 90° · 2 sets  ✦</t>
         </is>
@@ -7869,44 +7858,44 @@
       </c>
     </row>
     <row r="37" ht="24" customHeight="1">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="B37" s="11" t="inlineStr">
         <is>
           <t>TEST: Ring/ Bar Chinup</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>PASS: 5 reps</t>
         </is>
       </c>
-      <c r="D37" s="15" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
         <is>
           <t>1–5 reps · 2 sets  ✦</t>
         </is>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="10" t="inlineStr">
         <is>
           <t>✦</t>
         </is>
       </c>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="B38" s="11" t="inlineStr">
         <is>
           <t>TEST: Ring/ Bar Pullups</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="12" t="inlineStr">
         <is>
           <t>PASS: 5 reps</t>
         </is>
       </c>
-      <c r="D38" s="15" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
         <is>
           <t>1–5 reps · 2 sets  ✦</t>
         </is>
